--- a/Team-Data/2014-15/2-21-2014-15.xlsx
+++ b/Team-Data/2014-15/2-21-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -799,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>15</v>
@@ -811,10 +878,10 @@
         <v>12</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
         <v>13</v>
@@ -969,13 +1036,13 @@
         <v>11</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -993,7 +1060,7 @@
         <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>6</v>
@@ -1142,7 +1209,7 @@
         <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>26</v>
@@ -1154,7 +1221,7 @@
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
         <v>16</v>
@@ -1166,16 +1233,16 @@
         <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" t="n">
         <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.415</v>
+        <v>0.423</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J5" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="K5" t="n">
         <v>0.422</v>
@@ -1234,31 +1301,31 @@
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N5" t="n">
         <v>0.308</v>
       </c>
       <c r="O5" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P5" t="n">
         <v>23.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="R5" t="n">
         <v>10.1</v>
       </c>
       <c r="S5" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T5" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V5" t="n">
         <v>11.8</v>
@@ -1267,25 +1334,25 @@
         <v>5.8</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z5" t="n">
         <v>18.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.5</v>
+        <v>94.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1318,7 +1385,7 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1330,10 +1397,10 @@
         <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>25</v>
@@ -1348,10 +1415,10 @@
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" t="n">
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J6" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L6" t="n">
         <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="P6" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R6" t="n">
         <v>12</v>
@@ -1437,10 +1504,10 @@
         <v>33.5</v>
       </c>
       <c r="T6" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="U6" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V6" t="n">
         <v>14.1</v>
@@ -1452,22 +1519,22 @@
         <v>6.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="AC6" t="n">
         <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
         <v>9</v>
@@ -1485,10 +1552,10 @@
         <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
@@ -1497,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,7 +1576,7 @@
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1518,10 +1585,10 @@
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
         <v>27</v>
@@ -1533,13 +1600,13 @@
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA6" t="n">
         <v>2</v>
       </c>
-      <c r="BA6" t="n">
-        <v>3</v>
-      </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1670,7 +1737,7 @@
         <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1679,7 +1746,7 @@
         <v>7</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
@@ -1694,7 +1761,7 @@
         <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
         <v>18</v>
@@ -1712,10 +1779,10 @@
         <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
         <v>37</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.661</v>
+        <v>0.649</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,40 +1838,40 @@
         <v>39.9</v>
       </c>
       <c r="J8" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.463</v>
       </c>
       <c r="L8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M8" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N8" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P8" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
         <v>12.5</v>
@@ -1822,13 +1889,13 @@
         <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1837,19 +1904,19 @@
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1864,22 +1931,22 @@
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ8" t="n">
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1900,13 +1967,13 @@
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
@@ -2028,13 +2095,13 @@
         <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
@@ -2055,25 +2122,25 @@
         <v>23</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
         <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
         <v>27</v>
@@ -2088,7 +2155,7 @@
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>18</v>
@@ -2252,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
         <v>19</v>
@@ -2264,7 +2331,7 @@
         <v>7</v>
       </c>
       <c r="BA10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2413,10 +2480,10 @@
         <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
@@ -2425,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -2496,76 +2563,76 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J12" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="M12" t="n">
         <v>33.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.718</v>
+        <v>0.716</v>
       </c>
       <c r="R12" t="n">
         <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>21.6</v>
       </c>
       <c r="V12" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.9</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
         <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
         <v>5</v>
@@ -2574,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
         <v>13</v>
@@ -2592,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
         <v>7</v>
@@ -2601,13 +2668,13 @@
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>14</v>
@@ -2616,22 +2683,22 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>18</v>
@@ -2753,7 +2820,7 @@
         <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2777,10 +2844,10 @@
         <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
         <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0.661</v>
+        <v>0.655</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J14" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,10 +2939,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="N14" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O14" t="n">
         <v>18.8</v>
@@ -2890,43 +2957,43 @@
         <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="T14" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U14" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="V14" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
         <v>7.9</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y14" t="n">
         <v>3.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.3</v>
+        <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
@@ -2983,13 +3050,13 @@
         <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
@@ -2998,7 +3065,7 @@
         <v>2</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>0.245</v>
+        <v>0.241</v>
       </c>
       <c r="H15" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M15" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.346</v>
+        <v>0.345</v>
       </c>
       <c r="O15" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="P15" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R15" t="n">
         <v>11.9</v>
       </c>
       <c r="S15" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="T15" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13</v>
@@ -3087,25 +3154,25 @@
         <v>7.2</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
         <v>4.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.9</v>
+        <v>-7.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,16 +3184,16 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
         <v>24</v>
@@ -3138,28 +3205,28 @@
         <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
       </c>
       <c r="AQ15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS15" t="n">
         <v>20</v>
       </c>
-      <c r="AR15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>17</v>
-      </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>23</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
         <v>19</v>
@@ -3168,13 +3235,13 @@
         <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,13 +3369,13 @@
         <v>1</v>
       </c>
       <c r="AI16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK16" t="n">
         <v>7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>28</v>
@@ -3341,7 +3408,7 @@
         <v>11</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>7</v>
@@ -3350,7 +3417,7 @@
         <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
@@ -3362,7 +3429,7 @@
         <v>14</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E17" t="n">
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" t="n">
-        <v>0.426</v>
+        <v>0.434</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
@@ -3418,34 +3485,34 @@
         <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.742</v>
       </c>
       <c r="R17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="U17" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W17" t="n">
         <v>8</v>
@@ -3460,16 +3527,16 @@
         <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
         <v>93.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
         <v>20</v>
@@ -3502,7 +3569,7 @@
         <v>17</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>13</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV17" t="n">
         <v>19</v>
@@ -3532,19 +3599,19 @@
         <v>24</v>
       </c>
       <c r="AY17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3663,7 +3730,7 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
         <v>11</v>
@@ -3693,10 +3760,10 @@
         <v>6</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3705,13 +3772,13 @@
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW18" t="n">
         <v>3</v>
       </c>
       <c r="AX18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY18" t="n">
         <v>12</v>
@@ -3720,7 +3787,7 @@
         <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3896,10 +3963,10 @@
         <v>27</v>
       </c>
       <c r="AY19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA19" t="n">
         <v>6</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -3952,61 +4019,61 @@
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>83.3</v>
+        <v>83.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L20" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
         <v>19.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O20" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
         <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.761</v>
       </c>
       <c r="R20" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S20" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
         <v>6.9</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
         <v>99.59999999999999</v>
@@ -4015,13 +4082,13 @@
         <v>-0.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>16</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
         <v>16</v>
@@ -4030,10 +4097,10 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>14</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>17</v>
       </c>
       <c r="AK20" t="n">
         <v>14</v>
@@ -4045,25 +4112,25 @@
         <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>17</v>
@@ -4075,13 +4142,13 @@
         <v>26</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AZ20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4254,7 +4321,7 @@
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -4301,61 +4368,61 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22" t="n">
         <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>0.545</v>
+        <v>0.537</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J22" t="n">
-        <v>85.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.444</v>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M22" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O22" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P22" t="n">
         <v>23.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R22" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S22" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="T22" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="U22" t="n">
         <v>20.3</v>
       </c>
       <c r="V22" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W22" t="n">
         <v>7.2</v>
@@ -4364,22 +4431,22 @@
         <v>6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA22" t="n">
         <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>100.9</v>
+        <v>100.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>14</v>
@@ -4391,10 +4458,10 @@
         <v>14</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4403,13 +4470,13 @@
         <v>20</v>
       </c>
       <c r="AL22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM22" t="n">
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
         <v>9</v>
@@ -4421,7 +4488,7 @@
         <v>16</v>
       </c>
       <c r="AR22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS22" t="n">
         <v>2</v>
@@ -4436,10 +4503,10 @@
         <v>23</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
@@ -4448,10 +4515,10 @@
         <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -4483,70 +4550,70 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>0.321</v>
+        <v>0.316</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
         <v>81.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O23" t="n">
         <v>14.1</v>
       </c>
       <c r="P23" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="Q23" t="n">
         <v>0.734</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
         <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
         <v>21.2</v>
@@ -4555,10 +4622,10 @@
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.7</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4582,7 +4649,7 @@
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>22</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,7 +4682,7 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>16</v>
@@ -4624,16 +4691,16 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
         <v>9</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4806,13 +4873,13 @@
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.518</v>
+        <v>0.527</v>
       </c>
       <c r="H25" t="n">
         <v>48.5</v>
       </c>
       <c r="I25" t="n">
-        <v>39.9</v>
+        <v>39.8</v>
       </c>
       <c r="J25" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.462</v>
+        <v>0.46</v>
       </c>
       <c r="L25" t="n">
         <v>9.5</v>
@@ -4880,25 +4947,25 @@
         <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="P25" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="R25" t="n">
         <v>10.8</v>
       </c>
       <c r="S25" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U25" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V25" t="n">
         <v>14.9</v>
@@ -4913,22 +4980,22 @@
         <v>4.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB25" t="n">
         <v>106</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4937,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI25" t="n">
         <v>3</v>
@@ -4946,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="AK25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>7</v>
@@ -4955,31 +5022,31 @@
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR25" t="n">
         <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV25" t="n">
         <v>21</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>22</v>
       </c>
       <c r="AW25" t="n">
         <v>5</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -5107,19 +5174,19 @@
         <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG26" t="n">
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>9</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5173,16 +5240,16 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -5211,43 +5278,43 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
         <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>80.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
         <v>15.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O27" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="P27" t="n">
-        <v>29.6</v>
+        <v>29.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.773</v>
@@ -5256,52 +5323,52 @@
         <v>11.1</v>
       </c>
       <c r="S27" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T27" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U27" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V27" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W27" t="n">
         <v>6.3</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AB27" t="n">
         <v>100.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.4</v>
+        <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,13 +5398,13 @@
         <v>8</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>5</v>
       </c>
       <c r="AT27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5352,7 +5419,7 @@
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
         <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>0.611</v>
+        <v>0.618</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,49 +5478,49 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.36</v>
+        <v>0.363</v>
       </c>
       <c r="O28" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
         <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T28" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U28" t="n">
         <v>24.5</v>
       </c>
       <c r="V28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W28" t="n">
         <v>7.6</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
@@ -5468,19 +5535,19 @@
         <v>100.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF28" t="n">
         <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH28" t="n">
         <v>2</v>
@@ -5489,10 +5556,10 @@
         <v>10</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL28" t="n">
         <v>11</v>
@@ -5501,31 +5568,31 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS28" t="n">
         <v>7</v>
       </c>
-      <c r="AO28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>6</v>
-      </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5534,7 +5601,7 @@
         <v>8</v>
       </c>
       <c r="AY28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ28" t="n">
         <v>10</v>
@@ -5543,7 +5610,7 @@
         <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -5575,85 +5642,85 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
         <v>37</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.673</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="J29" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.454</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O29" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P29" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q29" t="n">
         <v>0.783</v>
       </c>
       <c r="R29" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S29" t="n">
         <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W29" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="X29" t="n">
         <v>4.6</v>
       </c>
       <c r="Y29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="AC29" t="n">
         <v>5.2</v>
       </c>
-      <c r="Z29" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>105.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -5665,16 +5732,16 @@
         <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5692,10 +5759,10 @@
         <v>4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS29" t="n">
         <v>26</v>
@@ -5707,16 +5774,16 @@
         <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ29" t="n">
         <v>23</v>
@@ -5728,7 +5795,7 @@
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
         <v>22</v>
@@ -5856,10 +5923,10 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM30" t="n">
         <v>17</v>
@@ -5868,7 +5935,7 @@
         <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
         <v>16</v>
@@ -5886,7 +5953,7 @@
         <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV30" t="n">
         <v>24</v>
@@ -5895,7 +5962,7 @@
         <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>17</v>
@@ -5907,7 +5974,7 @@
         <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF31" t="n">
         <v>11</v>
@@ -6029,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>6</v>
@@ -6077,16 +6144,16 @@
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-21-2014-15</t>
+          <t>2015-02-21</t>
         </is>
       </c>
     </row>
